--- a/docs/review/packs/chapter-3.6.xlsx
+++ b/docs/review/packs/chapter-3.6.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -2284,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Preserve the peripheral third preferentially, since it carries most of the tension.</t>
+          <t>State it as a load path.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat a radial tear's depth as the mechanical variable rather than its length.</t>
+          <t>Preserve the peripheral third preferentially, since it carries most of the tension.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Expect a flattened or degenerate meniscus to convert less compression into tension.</t>
+          <t>Treat a radial tear's depth as the mechanical variable rather than its length.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat hoop tension as the quantity every meniscal operation is judged against.</t>
+          <t>Read a root avulsion as a complete failure of the tension path.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Repair construct and its orientation, since a suture across the fibres restores the path and one along them does not.</t>
+          <t>Expect a flattened or degenerate meniscus to convert less compression into tension.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Alignment and load, which determine the tension the restored path must carry.</t>
+          <t>Treat hoop tension as the quantity every meniscal operation is judged against.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Expect healed appearance and restored tension to differ, and judge by outcome.</t>
+          <t>Repair construct and its orientation, since a suture across the fibres restores the path and one along them does not.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Repair a root to its anatomic position, since tension depends on where the anchor sits.</t>
+          <t>Alignment and load, which determine the tension the restored path must carry.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2698,22 +2698,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.6.3-P1</t>
+          <t>3.6.2-P9</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.6.3</t>
+          <t>3.6.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Treat tear orientation relative to the circumferential fibres as the mechanical question.</t>
+          <t>Decide repairability from whether the tension path can be restored.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2723,22 +2723,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.6.3-P2</t>
+          <t>3.6.2-P10</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.6.3</t>
+          <t>3.6.2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Expect the inner third to behave more like cartilage and the outer like tendon.</t>
+          <t>Expect healed appearance and restored tension to differ, and judge by outcome.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2748,12 +2748,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.6.3-P3</t>
+          <t>3.6.2-P11</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.6.3</t>
+          <t>3.6.2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Treat the fibre architecture as the thing a repair either reconstitutes or does not.</t>
+          <t>Repair a root to its anatomic position, since tension depends on where the anchor sits.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.6.3-P4</t>
+          <t>3.6.3-P1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Expect repair in degenerate tissue to behave differently from repair in healthy tissue.</t>
+          <t>State a direction with any mechanical property of the meniscus.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P1</t>
+          <t>3.6.3-P2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Expect a longitudinal tear to be commoner because it fails the weaker direction.</t>
+          <t>Treat tear orientation relative to the circumferential fibres as the mechanical question.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2823,12 +2823,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P2</t>
+          <t>3.6.3-P3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Treat loss of shape under load as a radial fibre problem as well as a hoop problem.</t>
+          <t>Expect the inner third to behave more like cartilage and the outer like tendon.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2848,12 +2848,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P3</t>
+          <t>3.6.3-P4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Use the tear pattern as evidence of which fibre system failed.</t>
+          <t>Read tensile data with the species and age of the tissue in mind.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P4</t>
+          <t>3.6.3-P5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Treat the two systems as two separate repair problems.</t>
+          <t>Treat the fibre architecture as the thing a repair either reconstitutes or does not.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2898,12 +2898,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P5</t>
+          <t>3.6.3-P6</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Expect a radial repair to be the harder problem, because the construct carries the hoop tension.</t>
+          <t>Read a construct study's failure mode as well as its failure load.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2923,12 +2923,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.6.4-P6</t>
+          <t>3.6.3-P7</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Protect load after a radial repair, on the ground that the construct is the tension path.</t>
+          <t>Expect repair in degenerate tissue to behave differently from repair in healthy tissue.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2948,12 +2948,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.6.5-P1</t>
+          <t>3.6.4-P1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Expect posterior horn pathology to dominate, given where the load sits in flexion.</t>
+          <t>Expect a longitudinal tear to be commoner because it fails the weaker direction.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2973,12 +2973,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.6.5-P2</t>
+          <t>3.6.4-P2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Treat extrusion as removing the meniscus from the share without removing tissue.</t>
+          <t>Read a horizontal cleavage tear as a cohesion failure, typically in degenerate tissue.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2998,22 +2998,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.6.5-P3</t>
+          <t>3.6.4-P3</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Treat the flexion dependence as the reason posterior horn work matters out of proportion to its size.</t>
+          <t>Treat loss of shape under load as a radial fibre problem as well as a hoop problem.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -3023,22 +3023,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.6.5-P4</t>
+          <t>3.6.4-P4</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Repair posterior roots on load path grounds rather than on symptoms alone.</t>
+          <t>Use the tear pattern as evidence of which fibre system failed.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -3048,12 +3048,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.6.5-P5</t>
+          <t>3.6.4-P5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Treat the deep flexion literature as thin and the mechanism as sound.</t>
+          <t>Treat the two systems as two separate repair problems.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -3073,22 +3073,22 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.6.6-P1</t>
+          <t>3.6.4-P6</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.6.6</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Expect the damping loss after meniscectomy to show in impact activities rather than in walking.</t>
+          <t>Expect a radial repair to be the harder problem, because the construct carries the hoop tension.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3098,22 +3098,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.6.6-P2</t>
+          <t>3.6.4-P7</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.6.6</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat muscle as the modifiable shock absorber when the meniscal contribution has been lost.</t>
+          <t>Protect load after a radial repair, on the ground that the construct is the tension path.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.6.6-P3</t>
+          <t>3.6.4-P8</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.6.6</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Treat damping as the meniscal function with the weakest quantitative evidence and a sound mechanism.</t>
+          <t>Read healing rates by tear pattern rather than in aggregate.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3148,22 +3148,22 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.6.6-P4</t>
+          <t>3.6.5-P1</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.6.6</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Expect a substitute not to reproduce native damping properties.</t>
+          <t>Expect posterior horn pathology to dominate, given where the load sits in flexion.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -3173,12 +3173,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.6.7-P1</t>
+          <t>3.6.5-P2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.6.7</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Expect raised contact stress to shift the lubrication regime unfavourably.</t>
+          <t>Read the share as a subtraction from a paired specimen rather than a direct measurement.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3198,12 +3198,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.6.7-P2</t>
+          <t>3.6.5-P3</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.6.7</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat synovial fluid changes after injury as part of the picture rather than a separate problem.</t>
+          <t>Treat extrusion as removing the meniscus from the share without removing tissue.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -3223,12 +3223,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.6.7-P3</t>
+          <t>3.6.5-P4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.6.7</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Treat lubrication as a mechanism to understand rather than a function to restore.</t>
+          <t>Treat the flexion dependence as the reason posterior horn work matters out of proportion to its size.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3248,12 +3248,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.6.7-P4</t>
+          <t>3.6.5-P5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.6.7</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Use lubrication to explain progression rather than to justify an operation.</t>
+          <t>Repair posterior roots on load path grounds rather than on symptoms alone.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -3273,22 +3273,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P1</t>
+          <t>3.6.5-P6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Expect proprioceptive deficit after meniscal injury and resection, and expect it to be hard to attribute.</t>
+          <t>Advise on deep flexion activity by what it loads, in a knee with posterior horn pathology.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3298,22 +3298,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P2</t>
+          <t>3.6.5-P7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Treat combined meniscal and cruciate injury as a larger sensory loss than either alone.</t>
+          <t>Treat the deep flexion literature as thin and the mechanism as sound.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -3323,22 +3323,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P3</t>
+          <t>3.6.6-P1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Treat the sensory function as an argument for preserving horns specifically, which coincides with the load bearing argument for the same tissue.</t>
+          <t>Expect the damping loss after meniscectomy to show in impact activities rather than in walking.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3348,22 +3348,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P4</t>
+          <t>3.6.6-P2</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>The sensory case does not need to carry weight on its own, and it should not be asked to.</t>
+          <t>Treat muscle as the modifiable shock absorber when the meniscal contribution has been lost.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -3373,12 +3373,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P5</t>
+          <t>3.6.6-P3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Preserve horns, where the load bearing and the sensory arguments agree.</t>
+          <t>Treat damping as the meniscal function with the weakest quantitative evidence and a sound mechanism.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -3398,12 +3398,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P6</t>
+          <t>3.6.6-P4</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Expect proprioceptive recovery after transplantation to be incomplete.</t>
+          <t>Advise on impact activity in a meniscus deficient knee on mechanistic grounds, and say so.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.6.8-P7</t>
+          <t>3.6.6-P5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Avoid resting a treatment argument on proprioception alone.</t>
+          <t>Expect a substitute not to reproduce native damping properties.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P1</t>
+          <t>3.6.7-P1</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Repair position relative to the native footprint centre.</t>
+          <t>Expect raised contact stress to shift the lubrication regime unfavourably.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3473,12 +3473,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P2</t>
+          <t>3.6.7-P2</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Repair to the footprint centre rather than aiming to cover the whole footprint.</t>
+          <t>Treat synovial fluid changes after injury as part of the picture rather than a separate problem.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3498,22 +3498,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P3</t>
+          <t>3.6.7-P3</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Expect a lateral root tear to behave less severely than a medial one, because of the meniscofemoral ligaments.</t>
+          <t>Treat lubrication as a mechanism to understand rather than a function to restore.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3523,12 +3523,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P4</t>
+          <t>3.6.7-P4</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Treat a root as a load bearing attachment with a position specification.</t>
+          <t>Use lubrication to explain progression rather than to justify an operation.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3548,12 +3548,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P5</t>
+          <t>3.6.7-P5</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Repair position relative to the native centre, which is the dominant variable.</t>
+          <t>State the absence of any confirming measurement when this function is raised.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P6</t>
+          <t>3.6.8-P1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Alignment, which sets the load the repaired root must carry.</t>
+          <t>Expect proprioceptive deficit after meniscal injury and resection, and expect it to be hard to attribute.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3598,22 +3598,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P7</t>
+          <t>3.6.8-P2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Repair a root anatomically, since position decides the mechanics more than fixation strength does.</t>
+          <t>Treat combined meniscal and cruciate injury as a larger sensory loss than either alone.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3623,22 +3623,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P8</t>
+          <t>3.6.8-P3</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel and root work together where they share bone.</t>
+          <t>Read joint position sense measurements with their poor reproducibility in mind.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3648,12 +3648,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.6.9-P9</t>
+          <t>3.6.8-P4</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.6.9</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Expect imaging to show position and healing rather than function.</t>
+          <t>Treat the sensory function as an argument for preserving horns specifically, which coincides with the load bearing argument for the same tissue.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3673,22 +3673,22 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P1</t>
+          <t>3.6.8-P5</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>The 3 millimetre threshold is a convention applied to a continuous measurement, and it should be treated as such.</t>
+          <t>The sensory case does not need to carry weight on its own, and it should not be asked to.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3698,22 +3698,22 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P2</t>
+          <t>3.6.8-P6</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Expect supine imaging to underestimate it, and consider loaded imaging where it matters.</t>
+          <t>Preserve horns, where the load bearing and the sensory arguments agree.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3723,22 +3723,22 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P3</t>
+          <t>3.6.8-P7</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Treat the 3 millimetre figure as a convention rather than a boundary.</t>
+          <t>Expect proprioceptive recovery after transplantation to be incomplete.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3748,22 +3748,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P4</t>
+          <t>3.6.8-P8</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Expect less extrusion laterally, given the meniscofemoral attachments.</t>
+          <t>Avoid resting a treatment argument on proprioception alone.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3773,22 +3773,22 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P5</t>
+          <t>3.6.9-P1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Treat extrusion as the outcome measure for whether a meniscus is working, in a field with no direct measurement of function.</t>
+          <t>Repair position relative to the native footprint centre.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3798,22 +3798,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P6</t>
+          <t>3.6.9-P2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Measure extrusion before and after meniscal surgery as the available proxy for function.</t>
+          <t>Repair to the footprint centre rather than aiming to cover the whole footprint.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3823,22 +3823,22 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.6.10-P7</t>
+          <t>3.6.9-P3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.6.10</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Prefer loaded imaging where the measurement will change a decision.</t>
+          <t>Expect a lateral root tear to behave less severely than a medial one, because of the meniscofemoral ligaments.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3848,22 +3848,22 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P1</t>
+          <t>3.6.9-P4</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Repair aims to restore the anchor, so position matters as much as strength.</t>
+          <t>Treat a root as a load bearing attachment with a position specification.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3873,22 +3873,22 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P2</t>
+          <t>3.6.9-P5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Expect a medial posterior root tear to behave worse than a lateral one.</t>
+          <t>Repair position relative to the native centre, which is the dominant variable.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3898,22 +3898,22 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P3</t>
+          <t>3.6.9-P6</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Use extrusion as the imaging sign that the mechanism has failed.</t>
+          <t>Alignment, which sets the load the repaired root must carry.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3923,12 +3923,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P4</t>
+          <t>3.6.9-P7</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Treat root repair as a joint preservation operation rather than a symptom operation, because the mechanical case is about what happens next rather than about pain now.</t>
+          <t>Repair a root anatomically, since position decides the mechanics more than fixation strength does.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3948,12 +3948,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P5</t>
+          <t>3.6.9-P8</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Repair position relative to the native footprint centre.</t>
+          <t>Plan tunnel and root work together where they share bone.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3973,12 +3973,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P6</t>
+          <t>3.6.9-P9</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Alignment correction, which sets the load the repair must carry.</t>
+          <t>Correct alignment where a repaired root would be overloaded.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3998,12 +3998,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P7</t>
+          <t>3.6.9-P10</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Repair anatomically to the footprint centre, since direction of tension depends on it.</t>
+          <t>Expect imaging to show position and healing rather than function.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -4023,22 +4023,22 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P8</t>
+          <t>3.6.10-P1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Assess and correct alignment alongside a root repair in a varus limb.</t>
+          <t>The 3 millimetre threshold is a convention applied to a continuous measurement, and it should be treated as such.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -4048,22 +4048,22 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P9</t>
+          <t>3.6.10-P2</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Measure residual extrusion postoperatively as the available proxy for restored function.</t>
+          <t>Read extrusion as a sign of hoop failure and look for the cause.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -4073,22 +4073,22 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.6.11-P10</t>
+          <t>3.6.10-P3</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>3.6.11</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>- The footprint centre must be restored to restore the direction of tension.</t>
+          <t>Expect supine imaging to underestimate it, and consider loaded imaging where it matters.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -4098,12 +4098,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P1</t>
+          <t>3.6.10-P4</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Repair of a radial tear requires the construct to carry hoop tension across the tear until healing, which is a larger demand than a longitudinal repair.</t>
+          <t>Treat the 3 millimetre figure as a convention rather than a boundary.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -4123,12 +4123,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P2</t>
+          <t>3.6.10-P5</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Assess the depth towards the rim rather than the length of a radial tear.</t>
+          <t>Expect less extrusion laterally, given the meniscofemoral attachments.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -4148,22 +4148,22 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P3</t>
+          <t>3.6.10-P6</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Treat a complete radial tear as mechanically equivalent to a root tear.</t>
+          <t>Treat extrusion as the outcome measure for whether a meniscus is working, in a field with no direct measurement of function.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -4173,22 +4173,22 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P4</t>
+          <t>3.6.10-P7</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Expect a radial repair to make larger demands of the construct than a longitudinal one.</t>
+          <t>Measure extrusion before and after meniscal surgery as the available proxy for function.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -4198,12 +4198,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P5</t>
+          <t>3.6.10-P8</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Treat the radial tear as the pattern where the repair decision has the most mechanical consequence and the least reliable healing.</t>
+          <t>Read persisting extrusion after root repair as the hoop not having been restored.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -4223,12 +4223,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>3.6.12-P6</t>
+          <t>3.6.10-P9</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>3.6.12</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Protect load after a radial repair, since the construct carries the tension.</t>
+          <t>Correct alignment, or a restored meniscus will extrude again.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -4248,22 +4248,22 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P1</t>
+          <t>3.6.10-P10</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>3.6.13</t>
+          <t>3.6.10</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Repair is preferred to resection because it preserves the load path, and the construct is what makes that possible.</t>
+          <t>Prefer loaded imaging where the measurement will change a decision.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -4273,22 +4273,22 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P2</t>
+          <t>3.6.11-P1</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>3.6.13</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Treat biological augmentation as addressing healing rather than fixation.</t>
+          <t>Repair aims to restore the anchor, so position matters as much as strength.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -4298,22 +4298,22 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P3</t>
+          <t>3.6.11-P2</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>3.6.13</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Treat the construct as one of three requirements, alongside tissue capable of healing and a mechanical environment that lets it.</t>
+          <t>Compare a root tear against total meniscectomy rather than against partial resection.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -4323,22 +4323,22 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P4</t>
+          <t>3.6.11-P3</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>3.6.13</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Identify which requirement is failing before deciding whether to repair at all.</t>
+          <t>Expect a medial posterior root tear to behave worse than a lateral one.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -4348,12 +4348,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P1</t>
+          <t>3.6.11-P4</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Expect contact mechanics to improve towards normal rather than reach it.</t>
+          <t>Use extrusion as the imaging sign that the mechanism has failed.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -4373,12 +4373,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P2</t>
+          <t>3.6.11-P5</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Treat transplantation as an area restoring operation with a partial tension restoring effect, and judge it on that rather than on being a meniscus replacement.</t>
+          <t>Treat root repair as a joint preservation operation rather than a symptom operation, because the mechanical case is about what happens next rather than about pain now.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -4398,22 +4398,22 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P3</t>
+          <t>3.6.11-P6</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Address alignment and instability first or simultaneously rather than afterwards.</t>
+          <t>Repair position relative to the native footprint centre.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4423,31 +4423,681 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P4</t>
+          <t>3.6.11-P7</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.11</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Expect a scaffold to restore area without reproducing the tensile architecture.</t>
+          <t>Alignment correction, which sets the load the repair must carry.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11-P8</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Repair anatomically to the footprint centre, since direction of tension depends on it.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11-P9</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Assess and correct alignment alongside a root repair in a varus limb.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11-P10</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Measure residual extrusion postoperatively as the available proxy for restored function.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11-P11</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>3.6.11</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>- The footprint centre must be restored to restore the direction of tension.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P1</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Repair of a radial tear requires the construct to carry hoop tension across the tear until healing, which is a larger demand than a longitudinal repair.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P2</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Assess the depth towards the rim rather than the length of a radial tear.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P3</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Treat a complete radial tear as mechanically equivalent to a root tear.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P4</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Expect a radial repair to make larger demands of the construct than a longitudinal one.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P5</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Treat the radial tear as the pattern where the repair decision has the most mechanical consequence and the least reliable healing.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P6</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Protect load after a radial repair, since the construct carries the tension.</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12-P7</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>3.6.12</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment where the construct would otherwise carry an excessive tension.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P1</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Repair is preferred to resection because it preserves the load path, and the construct is what makes that possible.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P2</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Read the failure mode to know whether the tissue or the construct was the limit.</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P3</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Treat biological augmentation as addressing healing rather than fixation.</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P4</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Treat the construct as one of three requirements, alongside tissue capable of healing and a mechanical environment that lets it.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P5</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment where it would load the repair excessively.</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P6</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Read reported healing rates with pattern, location and concurrent procedure attached.</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P7</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Identify which requirement is failing before deciding whether to repair at all.</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13-P8</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>3.6.13</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Set the aim by cartilage state rather than by tear repairability alone.</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P1</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Monitor extrusion postoperatively as the proxy for function.</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P2</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Expect contact mechanics to improve towards normal rather than reach it.</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P3</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Treat transplantation as an area restoring operation with a partial tension restoring effect, and judge it on that rather than on being a meniscus replacement.</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P4</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment and instability before or with a transplant.</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P5</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Set the indication by compartment specific symptoms in a deficient compartment.</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P6</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Address alignment and instability first or simultaneously rather than afterwards.</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P7</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Expect a scaffold to restore area without reproducing the tensile architecture.</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4778,7 +5428,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>83</f>
+        <f>109</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -4793,7 +5443,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E85,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E111,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -4823,7 +5473,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E85,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E111,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -4835,7 +5485,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E85,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E111,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -4847,7 +5497,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E85,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E111,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4859,7 +5509,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E85,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E111,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.6.xlsx
+++ b/docs/review/packs/chapter-3.6.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -2284,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment where the construct would otherwise carry an excessive tension.</t>
+          <t>Counsel on lower healing rates for this pattern, with the mechanical reason.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
@@ -4723,22 +4723,22 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P1</t>
+          <t>3.6.12-P8</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>3.6.13</t>
+          <t>3.6.12</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Repair is preferred to resection because it preserves the load path, and the construct is what makes that possible.</t>
+          <t>Correct alignment where the construct would otherwise carry an excessive tension.</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
@@ -4748,7 +4748,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P2</t>
+          <t>3.6.13-P1</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Read the failure mode to know whether the tissue or the construct was the limit.</t>
+          <t>Repair is preferred to resection because it preserves the load path, and the construct is what makes that possible.</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P3</t>
+          <t>3.6.13-P2</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Treat biological augmentation as addressing healing rather than fixation.</t>
+          <t>Read the failure mode to know whether the tissue or the construct was the limit.</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P4</t>
+          <t>3.6.13-P3</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Treat the construct as one of three requirements, alongside tissue capable of healing and a mechanical environment that lets it.</t>
+          <t>Treat biological augmentation as addressing healing rather than fixation.</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -4823,7 +4823,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P5</t>
+          <t>3.6.13-P4</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment where it would load the repair excessively.</t>
+          <t>Treat the construct as one of three requirements, alongside tissue capable of healing and a mechanical environment that lets it.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -4848,7 +4848,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P6</t>
+          <t>3.6.13-P5</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Read reported healing rates with pattern, location and concurrent procedure attached.</t>
+          <t>Correct alignment where it would load the repair excessively.</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P7</t>
+          <t>3.6.13-P6</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Identify which requirement is failing before deciding whether to repair at all.</t>
+          <t>Read reported healing rates with pattern, location and concurrent procedure attached.</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>3.6.13-P8</t>
+          <t>3.6.13-P7</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Set the aim by cartilage state rather than by tear repairability alone.</t>
+          <t>Identify which requirement is failing before deciding whether to repair at all.</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
@@ -4923,22 +4923,22 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P1</t>
+          <t>3.6.13-P8</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.13</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Monitor extrusion postoperatively as the proxy for function.</t>
+          <t>Set the aim by cartilage state rather than by tear repairability alone.</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -4948,22 +4948,22 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P2</t>
+          <t>3.6.13-P9</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>3.6.14</t>
+          <t>3.6.13</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Expect contact mechanics to improve towards normal rather than reach it.</t>
+          <t>Share the uncertainty, since no measurement predicts the individual result.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -4973,7 +4973,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P3</t>
+          <t>3.6.14-P1</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Treat transplantation as an area restoring operation with a partial tension restoring effect, and judge it on that rather than on being a meniscus replacement.</t>
+          <t>Monitor extrusion postoperatively as the proxy for function.</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P4</t>
+          <t>3.6.14-P2</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment and instability before or with a transplant.</t>
+          <t>Expect contact mechanics to improve towards normal rather than reach it.</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P5</t>
+          <t>3.6.14-P3</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Set the indication by compartment specific symptoms in a deficient compartment.</t>
+          <t>Treat transplantation as an area restoring operation with a partial tension restoring effect, and judge it on that rather than on being a meniscus replacement.</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
@@ -5048,7 +5048,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P6</t>
+          <t>3.6.14-P4</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Address alignment and instability first or simultaneously rather than afterwards.</t>
+          <t>Correct alignment and instability before or with a transplant.</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>3.6.14-P7</t>
+          <t>3.6.14-P5</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -5083,21 +5083,96 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Expect a scaffold to restore area without reproducing the tensile architecture.</t>
+          <t>Set the indication by compartment specific symptoms in a deficient compartment.</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P6</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Counsel on symptom relief separately from cartilage protection.</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P7</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Address alignment and instability first or simultaneously rather than afterwards.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14-P8</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>3.6.14</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Expect a scaffold to restore area without reproducing the tensile architecture.</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5428,7 +5503,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>109</f>
+        <f>112</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -5443,7 +5518,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E111,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E114,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -5473,7 +5548,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E111,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E114,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -5485,7 +5560,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E111,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E114,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5497,7 +5572,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E111,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E114,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -5509,7 +5584,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E111,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E114,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
